--- a/ixigo-flightBooking-API/src/test/resources/testData/Ixigo.xlsx
+++ b/ixigo-flightBooking-API/src/test/resources/testData/Ixigo.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{0563556B-4E6B-47D1-AA81-ADB289550163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mkesavareddygari\git\IAP_ixigo-flightBooking_API\ixigo-flightBooking-API\src\test\resources\testData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C4E774-3774-4E74-A472-D0DAED42F95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{DFC0FF53-8E93-496E-93C1-68054A271D52}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="8170" activeTab="1" xr2:uid="{DFC0FF53-8E93-496E-93C1-68054A271D52}"/>
   </bookViews>
   <sheets>
     <sheet name="QA" sheetId="1" r:id="rId1"/>
     <sheet name="APITestData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
   <si>
     <t>SourceCity</t>
   </si>
@@ -57,199 +58,133 @@
     <t>Password</t>
   </si>
   <si>
+    <t>TestName</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>Chennai International Airport</t>
+  </si>
+  <si>
+    <t>Book the flight ticket from Chennai to Mumbai</t>
+  </si>
+  <si>
+    <t>Mumbai Chhatrapati Shivaji International Airport</t>
+  </si>
+  <si>
+    <t>TestCase</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Job</t>
+  </si>
+  <si>
+    <t>CreateAndGetUser</t>
+  </si>
+  <si>
+    <t>Dhanunjaya</t>
+  </si>
+  <si>
+    <t>QA Engineer</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>EmptyPostRequest</t>
+  </si>
+  <si>
+    <t>PostStatusCode</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>PostResponseJob</t>
+  </si>
+  <si>
+    <t>PostResponseName</t>
+  </si>
+  <si>
+    <t>CreatedAt</t>
+  </si>
+  <si>
+    <t>ResponseId</t>
+  </si>
+  <si>
+    <t>GetStatusCode</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>GetUserFirstName</t>
+  </si>
+  <si>
+    <t>Janet</t>
+  </si>
+  <si>
+    <t>GetUserEmail</t>
+  </si>
+  <si>
+    <t>janet.weaver@reqres.in</t>
+  </si>
+  <si>
+    <t>GetUserLastName</t>
+  </si>
+  <si>
+    <t>Weaver</t>
+  </si>
+  <si>
+    <t>GetResponseBody</t>
+  </si>
+  <si>
+    <t>{"data":{"id":2,"email":"janet.weaver@reqres.in","first_name":"Janet","last_name":"Weaver","avatar":"https://reqres.in/img/faces/2-image.jpg"},"support":{"url":"https://benhowdle.im/first-cto-playbook?utm_source=reqres&amp;utm_medium=json&amp;utm_campaign=referral","text":"Become a better CTO. A playbook of painful stories and practical advice from a two-time startup CTO."},"_meta":{"powered_by":"ReqRes","docs_url":"https://app.reqres.in/documentation","upgrade_url":"https://app.reqres.in/upgrade","example_url":"https://app.reqres.in/examples/notes-app","variant":"v1_b","message":"This is a read-only demo endpoint. Sign up to create your own collections with full CRUD and auth.","cta":{"label":"Get started","url":"https://app.reqres.in/upgrade"},"context":"legacy_success"}}</t>
+  </si>
+  <si>
+    <t>PostResponseBody</t>
+  </si>
+  <si>
+    <t>InvalidUserId</t>
+  </si>
+  <si>
+    <t>GetNonExistentUser</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>2026-06-13T19:39:30.071Z</t>
+  </si>
+  <si>
+    <t>551</t>
+  </si>
+  <si>
+    <t>{"id":"87","createdAt":"2026-06-13T19:39:32.472Z","_meta":{"powered_by":"ReqRes","docs_url":"https://app.reqres.in/documentation","upgrade_url":"https://app.reqres.in/upgrade","example_url":"https://app.reqres.in/examples/notes-app","variant":"v1_b","message":"This is a read-only demo endpoint. Sign up to create your own collections with full CRUD and auth.","cta":{"label":"Get started","url":"https://app.reqres.in/upgrade"},"context":"legacy_success"}}</t>
+  </si>
+  <si>
+    <t>kmadhavi1811@gmail.com</t>
+  </si>
+  <si>
     <t>Hanvi@20180422</t>
   </si>
   <si>
-    <t>TestName</t>
-  </si>
-  <si>
-    <t>test2</t>
-  </si>
-  <si>
-    <t>test3</t>
-  </si>
-  <si>
-    <t>test4</t>
-  </si>
-  <si>
-    <t>Pune</t>
-  </si>
-  <si>
-    <t>Pune International Airport</t>
-  </si>
-  <si>
-    <t>Mumbai International Airport</t>
-  </si>
-  <si>
-    <t>Mumbai</t>
-  </si>
-  <si>
-    <t>Delhi</t>
-  </si>
-  <si>
-    <t>Indra Gandhi International Airport</t>
-  </si>
-  <si>
-    <t>Kochi</t>
-  </si>
-  <si>
-    <t>Kochi International Airport</t>
-  </si>
-  <si>
-    <t>Chennai</t>
-  </si>
-  <si>
-    <t>Chennai International Airport</t>
-  </si>
-  <si>
-    <t>Book the flight ticket from Banglore to Hyderabad</t>
-  </si>
-  <si>
-    <t>Book the flight ticket from Chennai to Mumbai</t>
-  </si>
-  <si>
-    <t>Mumbai Chhatrapati Shivaji International Airport</t>
-  </si>
-  <si>
-    <t>TestCase</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Job</t>
-  </si>
-  <si>
-    <t>CreateAndGetUser</t>
-  </si>
-  <si>
-    <t>QA Engineer</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>EmptyPostRequest</t>
-  </si>
-  <si>
-    <t>PostStatusCode</t>
-  </si>
-  <si>
-    <t>PostResponseJob</t>
-  </si>
-  <si>
-    <t>PostResponseName</t>
-  </si>
-  <si>
-    <t>CreatedAt</t>
-  </si>
-  <si>
-    <t>ResponseId</t>
-  </si>
-  <si>
-    <t>GetStatusCode</t>
-  </si>
-  <si>
-    <t>GetUserFirstName</t>
-  </si>
-  <si>
-    <t>GetUserEmail</t>
-  </si>
-  <si>
-    <t>GetUserLastName</t>
-  </si>
-  <si>
-    <t>GetResponseBody</t>
-  </si>
-  <si>
-    <t>PostResponseBody</t>
-  </si>
-  <si>
-    <t>kmadhavi1811@gmail.com</t>
-  </si>
-  <si>
-    <t>Madhavi</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>2026-06-15T03:03:09.522Z</t>
-  </si>
-  <si>
-    <t>839</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Janet</t>
-  </si>
-  <si>
-    <t>janet.weaver@reqres.in</t>
-  </si>
-  <si>
-    <t>Weaver</t>
-  </si>
-  <si>
-    <t>{"data":{"id":2,"email":"janet.weaver@reqres.in","first_name":"Janet","last_name":"Weaver","avatar":"https://reqres.in/img/faces/2-image.jpg"},"support":{"url":"https://benhowdle.im/first-cto-playbook?utm_source=reqres&amp;utm_medium=json&amp;utm_campaign=referral","text":"Become a better CTO. A playbook of painful stories and practical advice from a two-time startup CTO."},"_meta":{"powered_by":"ReqRes","docs_url":"https://app.reqres.in/documentation","upgrade_url":"https://app.reqres.in/upgrade","example_url":"https://app.reqres.in/examples/notes-app","variant":"v1_b","message":"This is a read-only demo endpoint. Sign up to create your own collections with full CRUD and auth.","cta":{"label":"Get started","url":"https://app.reqres.in/upgrade"},"context":"legacy_success"}}</t>
-  </si>
-  <si>
-    <t>{"id":"613","createdAt":"2026-06-15T03:03:11.267Z","_meta":{"powered_by":"ReqRes","docs_url":"https://app.reqres.in/documentation","upgrade_url":"https://app.reqres.in/upgrade","example_url":"https://app.reqres.in/examples/notes-app","variant":"v1_b","message":"This is a read-only demo endpoint. Sign up to create your own collections with full CRUD and auth.","cta":{"label":"Get started","url":"https://app.reqres.in/upgrade"},"context":"legacy_success"}}</t>
-  </si>
-  <si>
-    <t>2026-06-15T12:46:30.692Z</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>{"id":"818","createdAt":"2026-06-15T12:46:33.101Z","_meta":{"powered_by":"ReqRes","docs_url":"https://app.reqres.in/documentation","upgrade_url":"https://app.reqres.in/upgrade","example_url":"https://app.reqres.in/examples/notes-app","variant":"v1_b","message":"This is a read-only demo endpoint. Sign up to create your own collections with full CRUD and auth.","cta":{"label":"Get started","url":"https://app.reqres.in/upgrade"},"context":"legacy_success"}}</t>
-  </si>
-  <si>
-    <t>2026-06-15T12:47:37.106Z</t>
-  </si>
-  <si>
-    <t>392</t>
-  </si>
-  <si>
-    <t>{"id":"236","createdAt":"2026-06-15T12:47:40.230Z","_meta":{"powered_by":"ReqRes","docs_url":"https://app.reqres.in/documentation","upgrade_url":"https://app.reqres.in/upgrade","example_url":"https://app.reqres.in/examples/notes-app","variant":"v1_b","message":"This is a read-only demo endpoint. Sign up to create your own collections with full CRUD and auth.","cta":{"label":"Get started","url":"https://app.reqres.in/upgrade"},"context":"legacy_success"}}</t>
-  </si>
-  <si>
-    <t>2026-06-15T14:00:57.057Z</t>
-  </si>
-  <si>
-    <t>951</t>
-  </si>
-  <si>
-    <t>{"id":"16","createdAt":"2026-06-15T14:00:59.783Z","_meta":{"powered_by":"ReqRes","docs_url":"https://app.reqres.in/documentation","upgrade_url":"https://app.reqres.in/upgrade","example_url":"https://app.reqres.in/examples/notes-app","variant":"v1_b","message":"This is a read-only demo endpoint. Sign up to create your own collections with full CRUD and auth.","cta":{"label":"Get started","url":"https://app.reqres.in/upgrade"},"context":"legacy_success"}}</t>
-  </si>
-  <si>
-    <t>2026-06-16T03:18:16.002Z</t>
-  </si>
-  <si>
-    <t>831</t>
-  </si>
-  <si>
-    <t>{"id":"655","createdAt":"2026-06-16T03:18:17.554Z","_meta":{"powered_by":"ReqRes","docs_url":"https://app.reqres.in/documentation","upgrade_url":"https://app.reqres.in/upgrade","example_url":"https://app.reqres.in/examples/notes-app","variant":"v1_b","message":"This is a read-only demo endpoint. Sign up to create your own collections with full CRUD and auth.","cta":{"label":"Get started","url":"https://app.reqres.in/upgrade"},"context":"legacy_success"}}</t>
-  </si>
-  <si>
-    <t>2026-06-19T02:00:25.274Z</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>{"id":"590","createdAt":"2026-06-19T02:00:27.482Z","_meta":{"powered_by":"ReqRes","docs_url":"https://app.reqres.in/documentation","upgrade_url":"https://app.reqres.in/upgrade","example_url":"https://app.reqres.in/examples/notes-app","variant":"v1_b","message":"This is a read-only demo endpoint. Sign up to create your own collections with full CRUD and auth.","cta":{"label":"Get started","url":"https://app.reqres.in/upgrade"},"context":"legacy_success"}}</t>
-  </si>
-  <si>
-    <t>2026-06-19T02:06:02.338Z</t>
-  </si>
-  <si>
-    <t>402</t>
-  </si>
-  <si>
-    <t>{"id":"935","createdAt":"2026-06-19T02:06:04.261Z","_meta":{"powered_by":"ReqRes","docs_url":"https://app.reqres.in/documentation","upgrade_url":"https://app.reqres.in/upgrade","example_url":"https://app.reqres.in/examples/notes-app","variant":"v1_b","message":"This is a read-only demo endpoint. Sign up to create your own collections with full CRUD and auth.","cta":{"label":"Get started","url":"https://app.reqres.in/upgrade"},"context":"legacy_success"}}</t>
+    <t>Book the flight ticket from Hyderabad to Banglore</t>
+  </si>
+  <si>
+    <t>2026-06-25T16:05:40.414Z</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>{"id":"118","createdAt":"2026-06-25T16:05:42.850Z","_meta":{"powered_by":"ReqRes","docs_url":"https://app.reqres.in/documentation","upgrade_url":"https://app.reqres.in/upgrade","example_url":"https://app.reqres.in/examples/notes-app","variant":"v1_b","message":"This is a read-only demo endpoint. Sign up to create your own collections with full CRUD and auth.","cta":{"label":"Get started","url":"https://app.reqres.in/upgrade"},"context":"legacy_success"}}</t>
   </si>
 </sst>
 </file>
@@ -633,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86214DA4-C899-4E03-9A09-CDA4A8300491}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="40.453125"/>
@@ -641,13 +576,13 @@
     <col min="3" max="3" bestFit="true" customWidth="true" width="27.453125"/>
     <col min="4" max="4" customWidth="true" width="17.36328125"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="28.36328125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="18.90625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="23.36328125"/>
     <col min="7" max="7" bestFit="true" customWidth="true" width="15.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>0</v>
@@ -670,7 +605,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>2</v>
@@ -685,112 +620,39 @@
         <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>3</v>
-      </c>
       <c r="C3" t="s" s="0">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{2BB6CA6E-C41E-4C5F-8EC8-62C009EC7280}"/>
-    <hyperlink ref="G2" r:id="rId2" xr:uid="{B941F73B-177F-49A1-A79E-7CCF263A10D9}"/>
-    <hyperlink ref="G3" r:id="rId3" xr:uid="{E09AB40C-9415-4FB5-B08F-F6E84EC52D4E}"/>
-    <hyperlink ref="G4" r:id="rId4" xr:uid="{920DF96A-7DAA-447D-857C-1495A8FD4E9F}"/>
-    <hyperlink ref="G5" r:id="rId5" xr:uid="{B48EC493-81EB-481F-95EF-F4155E5BC315}"/>
-    <hyperlink ref="G6" r:id="rId6" xr:uid="{2772FE30-E1BF-480B-BB73-31102E366BE8}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{BBDAEC1F-4169-4FF6-A108-E621CD2DC49E}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{ABE63B8A-34F7-4771-AFF8-C28AF3B56702}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -798,114 +660,138 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="16.26953125"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="17.26953125"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="10.453125"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="11.26953125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.36328125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="H1" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="I1" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="J1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="D1" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="E1" t="s" s="0">
+      <c r="K1" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="M1" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="F1" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="G1" t="s" s="0">
+      <c r="N1" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="H1" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="I1" t="s" s="0">
+      <c r="O1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="J1" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="K1" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="L1" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="M1" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>45</v>
-      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>51</v>
       </c>
       <c r="J2" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="O3" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="K2" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="L2" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>55</v>
-      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>48</v>
-      </c>
-      <c r="N3" t="s" s="0">
-        <v>74</v>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
